--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2022_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_prebrut_a_2022_antofagasta.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:34</t>
+    <t xml:space="preserve">2026-09-24 01:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.03</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.37</v>
@@ -762,7 +762,7 @@
         <v>0.03</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.6</v>
@@ -785,7 +785,7 @@
         <v>0.02</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.1</v>
@@ -799,7 +799,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>6</v>
@@ -808,7 +808,7 @@
         <v>0.01</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.27</v>
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.85</v>
+        <v>-0.27</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>309</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.96</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +868,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>6</v>
@@ -880,7 +880,7 @@
         <v>309</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.85</v>
+        <v>0.69</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>309</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.71</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="18">
